--- a/Niche-Product-Longlist.xlsx
+++ b/Niche-Product-Longlist.xlsx
@@ -8,16 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Long-List Scorecard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Demand Data" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="SERP Winnability" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Benchmarks" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Scorecard v2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Long-tail Evidence" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Live SERP Checks" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Demand Data (v1)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Benchmarks" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Long-List Scorecard'!$A$1:$N$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Demand Data'!$A$1:$G$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'SERP Winnability'!$A$1:$D$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Benchmarks'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Scorecard v2'!$A$1:$N$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Long-tail Evidence'!$A$1:$F$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live SERP Checks'!$A$1:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Demand Data (v1)'!$A$1:$G$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Benchmarks'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -69,7 +71,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +96,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -123,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -174,6 +181,15 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -542,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -551,14 +567,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Niche Product Long-List — golfweights.co.uk-style ecommerce opportunities</t>
+          <t>Niche Product Long-List v2 — blue-ocean re-rank</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prepared for Joe (Sabroso Studio) · August 2026 · Data: Ahrefs (GB + US), SERP overviews, live site checks</t>
+          <t>Prepared for Joe (Sabroso Studio) · August 2026 · Data: Ahrefs GB+US, long-tail matching-terms pulls, LIVE Google UK SERPs (SERPAPI)</t>
         </is>
       </c>
     </row>
@@ -568,182 +584,145 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>THE BRIEF</t>
+          <t>WHAT CHANGED FROM v1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Find products that scale the way golfweights.co.uk does: cheap to make, near-free to ship, sold to enthusiasts with disposable income, with a brand × model compatibility matrix that generates hundreds of specific, winnable keywords — OR products where a UK supplier already holds stock/fulfilment and the whole opportunity is building the owned front-end + SEO (the lifebuoysdirect.co.uk / white-label coffee pattern).</t>
+          <t>1. Blue-ocean test tightened: 'ropey competitors on page 1' still means the SERP is occupied. v2 grades SERP openness from LIVE Google UK results (not Ahrefs cache), counting dedicated specialists on page 1. golf club weights = ~zero specialists; that's the bar.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2. Bias shifted to archetype B (supplier-unaware) and higher-ticket products, away from AliExpress FMCG-adjacent.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>TWO SOURCING ARCHETYPES</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>3. Long-tail enumerated per angle (see Long-tail Evidence tab) instead of head terms only — including flagging AI-synthetic keyword families that inflate Ahrefs volumes (e.g. 'cricket pitch protection covers {city}' ×10, 'custom brass gym flooring').</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>A — China import: AliExpress/Alibaba commodity, you hold cheap stock, letter-post shipping. Moat = catalogue depth + SEO + UK trust.</t>
+          <t>4. v1 leaders re-graded down on live competition: headphone pads (Wicked Cushions + Amazon/eBay churn is real), blind spares (three 'blind spares/parts'-named specialists on page 1).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>B — UK supplier front-end: importer/manufacturer/wholesaler with the product but a ropey or non-consumer web presence. You build brand + ecommerce + SEO; they hold stock and ship. Near-zero capital; moat = supply relationship + search dominance. Consumables (coffee, dog food) add repeat revenue this archetype uniquely enables.</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>THE KEY META-FINDING</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>CALIBRATION — WHAT 'WORKING' LOOKS LIKE (see Benchmarks tab)</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Genuinely empty SERPs are now rare — every 'obvious' bold angle probed live (vee belts, arena mirrors, cricket covers, made-to-measure netting, changing-room benches, padel canopies) turned out to be colonised, sometimes by 6-8 specialists in a micro-niche. The reliable blue-ocean signal is SERP MIS-SERVICE: Google substituting the wrong product because no correct page exists. 'gym mats with logo' returns entrance DOORMAT printers — the £10k branded sports-matting intent has no home. That substitution pattern is what to scan for, and it is how golf weights looks too (info pages substituting for a shop).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>lifebuoysdirect.co.uk ranks for only ~99 keywords and ~1,800 GB visits/month — yet reportedly turns over tens of thousands/month. golfweights.co.uk: ~400 visits/month. The bar is NOT big traffic; it is total domination of a small, high-intent SERP set. Ideas here with 200–1,500/mo aggregate demand clear that bar.</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>SCORING (each 1–5, higher = better; total /30)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>SCORING (each 1–5, higher = better)</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Demand · Matrix depth · SERP openness (live-checked where marked) · Economics &amp; ticket size · Repeat purchase · Supply ease.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Demand — GB-weighted aggregate search demand across the cluster (US used as structural sample).</t>
+          <t>CAP RULE: ≤2 on Matrix or SERP openness caps the idea at Tier B/C regardless of total (pink rows).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Matrix — depth of the brand × model × spec keyword/SKU matrix. The core golf-weights ingredient.</t>
+          <t>Tier A (green) = open-or-mis-served SERP with validated demand. Tier B (amber) = real but a named blocker. Tier C = weak or already owned.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Competition weakness — 5 = ropey dropshippers/no specialist; 1 = formalised specialist or Amazon/OEM owns the SERPs.</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Economics &amp; postage — letter-post-ability, margin structure, regulatory drag.</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>CALIBRATION (unchanged — see Benchmarks tab)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Repeat purchase — consumable/wear-part dynamics (LTV).</t>
+          <t>lifebuoysdirect.co.uk: 99 keywords, 52 top-3, ~1,800 visits/mo → tens of £k/mo. The bar is domination of a tiny high-intent SERP set.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Supply ease — commodity availability (A) or plausibility of a willing UK supplier (B).</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CAP RULE: any idea scoring ≤2 on Matrix or Competition is capped at Tier B/C regardless of total — those two are dealbreakers in this model. Capped rows are tinted pink in the scorecard.</t>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>SUGGESTED NEXT STEPS</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>1. Branded sports matting: supplier scouting (UK mat importers + dye-sub/large-format printers; judo/MMA mat importers), then a demand-shaping site targeting the adjacent funnel (commercial gym flooring 500/mo KD0 + custom yoga mats + boxing ring canvas + platforms) with quote-led UX.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>TIERS</t>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2. Validate caravan/motorhome locker hardware (the strongest unvalidated Tier A) — matching-terms on key codes + live SERPs.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Tier A (green) — validated with Ahrefs + SERP data, or near-validated; pursue first. Tier B (amber) — real but with a named blocker. Tier C — pattern-matched but weak on data or already owned.</t>
+          <t>3. Hot tub filters remains the best 'certain' play from v1 — specialist-free live SERP worth confirming, consumable revenue.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>4. Run the 'mis-served SERP' scan as a repeatable method: list quote-led B2B products sold via generic retailers, live-check whether Google substitutes; each substitution is a candidate.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>VALIDATION STATUS</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>'Validated' = GB+US keyword metrics pulled and GB SERP ownership checked (see Demand Data + SERP Winnability tabs). 'Inferred' = scored on judgement/pattern only — validate before acting. Volumes are Ahrefs 12-month averages (seasonality hidden). All CPC figures converted to USD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>THE UNRANKED PATTERN — WHITE-LABEL CONSUMABLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Your coffee-roaster and raw-dog-food examples don't rank on a keyword scorecard because the opportunity is supplier-led, not demand-led: find a UK producer with spare capacity and a good range, wrap a brand + site around them, they fulfil. The equivalent next step is supplier scouting (trade directories, wholesale marketplaces, Companies House) rather than keyword research. Candidate categories with proven demand: coffee, pet food/treats, candles/wax melts, hot sauce, protein/supplements, bird food. Happy to run that scouting exercise as a follow-up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>SUGGESTED NEXT STEP</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Pick 2–3 Tier A ideas → full playbook validation: matching-terms expansion (GB+US), full SERP/cannibalisation pass, supplier scouting, and a v1 site architecture. ~15–30k Ahrefs units per idea. This long-list consumed ~3.5k units.</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>~12k Ahrefs units spent in v2 (15.5k total project).</t>
         </is>
       </c>
     </row>
@@ -758,23 +737,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="70" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="72" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -810,17 +789,17 @@
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
-          <t>Competition weakness</t>
+          <t>SERP openness</t>
         </is>
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>Economics &amp; postage</t>
+          <t>Economics &amp; ticket</t>
         </is>
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>Repeat purchase</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
@@ -840,7 +819,7 @@
       </c>
       <c r="M1" s="4" t="inlineStr">
         <is>
-          <t>Validated?</t>
+          <t>Evidence status</t>
         </is>
       </c>
       <c r="N1" s="4" t="inlineStr">
@@ -855,39 +834,39 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Headphone replacement ear pads, cables &amp; headbands by model</t>
+          <t>Hot tub &amp; spa filters by brand / model / filter code</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A/B</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AliExpress commodity; fits Sony/Bose/Sennheiser/AKG/Beats × model. Letter-post.</t>
+          <t>Chinese filter converters or UK pool-trade wholesaler; Lay-Z-Spa/Intex/Wave/MSpa × model × code.</t>
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>4</v>
       </c>
       <c r="H2" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="I2" s="7" t="n">
+      <c r="J2" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="J2" s="7" t="n">
-        <v>5</v>
-      </c>
       <c r="K2" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -896,12 +875,12 @@
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
-          <t>Validated (GB+US)</t>
+          <t>Validated (GB+US + SERP)</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
-          <t>GB per-term volumes thin (replacement ear pads 40, headphone ear pads 70) but the US #1 page's traffic potential is ~3,000 — the long-tail matrix is where the demand lives, exactly like golf weights. GB SERP: US brand wickedcushions.com at #1 (proves the model), then generalists (Headset Store, Lindy, Amazon) — no UK model-matrix specialist. The closest true golf-weights clone on this list.</t>
+          <t>The highest-certainty play. 1,100/mo GB KD0 (+lay z spa 350; US 1,300 @ $0.60 CPC). SERP = hot-tub dealers' afterthought category pages, no dedicated filter specialist. True consumable (2-4/yr per owner). Not re-live-checked in v2 — do so before committing, given how often 'open' niches proved colonised.</t>
         </is>
       </c>
     </row>
@@ -911,21 +890,21 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Blind spare parts (roller / vertical / venetian / Velux) by system &amp; brand</t>
+          <t>Printed &amp; branded sports matting and facility branding (jigsaw mats with centre logos, judo/MMA mats, boxing ring canvases, platform inlays, branded gym flooring)</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>B/A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>UK component wholesalers (Louvolite/Decora trade lines) or AliExpress; chains, brackets, wands, carriers. Large-letter.</t>
+          <t>UK mat importer + large-format/dye-sub printer partnership (or a printer who already prints mats for trade). Quote-led, £2k-£15k tickets. Joe's tip — validated as mis-served.</t>
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="7" t="n">
         <v>4</v>
@@ -934,7 +913,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" s="7" t="n">
         <v>3</v>
@@ -943,7 +922,7 @@
         <v>4</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -952,12 +931,12 @@
       </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>Validated (GB+US)</t>
+          <t>Validated (live SERP + GB pulls)</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
-          <t>GB cluster ~700/mo (vertical blind parts 350, roller blind parts 200, blind spare parts 150), KD 0–32; #1 page traffic potential ~1,400. SERP is split across five+ visibly dated micro-sites (blindparts.co.uk still runs .asp URLs; US sites rank in GB for vertical terms) — classic fragmented-and-ropey competition. Distress-purchase intent converts hard.</t>
+          <t>THE BLUE-OCEAN PICK. Live Google UK for 'gym mats with logo' / 'branded gym mats' returns entrance DOORMAT printers and generic flooring shops — Google is substituting the wrong product because no specialist exists. Adjacent funnel demand is real: commercial gym flooring 500/mo KD0 @ $1.40 CPC, custom/branded/personalised yoga mats ~460/mo combined, boxing ring canvas 150, weightlifting platform 250. Direct terms ('custom wrestling mats', 'branded gym flooring') show 0 volume — nobody searches what nobody sells; demand is currently expressed through generic terms + trade word-of-mouth. Build = rank for the generic funnel, convert to quote.</t>
         </is>
       </c>
     </row>
@@ -967,7 +946,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Hot tub &amp; spa filters by brand / model / filter code</t>
+          <t>Caravan &amp; motorhome locker keys, catches, hinges &amp; vents by model / key code</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -977,11 +956,11 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Chinese filter converters or UK pool-trade wholesaler; matrix = Lay-Z-Spa/Intex/Wave/MSpa × model × code.</t>
+          <t>Key-by-code + catch-by-model matrix (Hartal/Dometic/Thetford/W4); AliExpress + UK leisure wholesalers. Letter-post.</t>
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="7" t="n">
         <v>4</v>
@@ -990,16 +969,16 @@
         <v>4</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>4</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1008,68 +987,68 @@
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>Validated (GB+US)</t>
+          <t>Inferred — validate next</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>hot tub filters 1,100/mo GB KD0 (+ lay z spa filters 350; US 1,300 with $0.60 CPC). GB SERP = hot-tub dealers' afterthought category pages — no dedicated filter specialist. True consumable (owners buy 2–4/yr) → repeat revenue the golf-weights model lacks. Slightly bulkier than letter-post, still light/cheap.</t>
+          <t>Strongest unvalidated candidate. Huge enthusiast base, distress purchases, key-code long-tail ('FW450 key'). Needs the v2 treatment before trusting: matching-terms on key codes + live SERP count.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Caravan &amp; motorhome locker keys, catches, hinges &amp; vents by model</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>A/B</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Key-by-code + catch-by-model matrix (Hartal/Dometic/Thetford/W4). AliExpress + UK leisure wholesalers. Letter-post.</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="7" t="n">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Ifor Williams &amp; trailer spares (dealer-partner front-end)</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Regional trailer dealer holds stock; you own the search front-end.</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="F5" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H5" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" s="7" t="n">
+      <c r="G5" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>Inferred — validate next</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>Not keyword-validated in this pass, but pattern-matches perfectly: huge enthusiast base, distress purchases, key-code long-tail ('FW450 key', 'hartal door lock'), competition = eBay churn + one or two dated sites (e.g. leisure spares generalists). First candidate for a follow-up validation.</t>
+      <c r="I5" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>Validated (GB + SERP)</t>
+        </is>
+      </c>
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>700/mo KD0 on the brand term; SERP = OEM page + weak regional dealers + eBay. Freight economics still the blocker; works only with dealer fulfilment.</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1058,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Drone propellers &amp; small spares by model (DJI et al.)</t>
+          <t>Drone propellers &amp; small spares by model</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -1089,7 +1068,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>AliExpress commodity; props/guards/hub kits by model. Letter-post perfect.</t>
+          <t>AliExpress; props/guards/hubs by model. Letter-post perfect.</t>
         </is>
       </c>
       <c r="E6" s="10" t="n">
@@ -1125,7 +1104,7 @@
       </c>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t>Each DJI model term does 80–200/mo GB (KD0) and the model list keeps growing; US double. Blockers: DJI sells direct and Amazon is strong — win the aftermarket/multi-pack angle. No UK specialist seen.</t>
+          <t>DJI model terms 80-200/mo GB each, KD0. DJI-direct + Amazon pressure; aftermarket/multi-pack angle.</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1114,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>E-scooter &amp; e-bike mechanical spares by model (tyres, tubes, brake pads, grips)</t>
+          <t>E-scooter &amp; e-bike mechanical spares by model</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -1145,7 +1124,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>AliExpress; fits Xiaomi/Segway/Pure/Brompton-adjacent. Avoid battery lines (regulatory).</t>
+          <t>Tyres, tubes, brake pads by model; avoid battery lines.</t>
         </is>
       </c>
       <c r="E7" s="10" t="n">
@@ -1176,12 +1155,12 @@
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>Inferred — validate next</t>
+          <t>Inferred</t>
         </is>
       </c>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t>Consumable wear parts + growing installed base + model matrix. Parcel not letter for tyres. Check SERPs: some specialists emerging; validate before committing.</t>
+          <t>Consumable + growing installed base. Not yet live-checked.</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1170,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Derailleur hangers &amp; model-specific bike smallparts</t>
+          <t>Headphone replacement ear pads, cables &amp; headbands by model</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -1201,11 +1180,11 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>AliExpress/Taiwan; hanger-by-frame-model is the canonical matrix product.</t>
+          <t>AliExpress; fits Sony/Bose/Sennheiser × model. Letter-post.</t>
         </is>
       </c>
       <c r="E8" s="13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>5</v>
@@ -1217,13 +1196,13 @@
         <v>5</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
@@ -1232,12 +1211,12 @@
       </c>
       <c r="M8" s="13" t="inlineStr">
         <is>
-          <t>Validated (GB+US)</t>
+          <t>Validated (GB+US + SERP) — DOWNGRADED v2</t>
         </is>
       </c>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>The biggest matrix demand found: GB 1,500/mo KD19, US 2,900 KD3. CAPPED: rearmechhanger.com already owns GB positions 1–2 — this niche's golf-weights already exists, plus Halfords. Only enter with a genuine angle (e.g. hangers bundled into a wider model-specific bike-smallparts matrix).</t>
+          <t>Still the best pure archetype-A matrix (US #1 page TP ~3,000), but re-graded on competition per Joe's read: Wicked Cushions is expanding, Amazon/eBay churn is heavy, Headset Store et al occupy the UK SERP. Openness 2 → capped. A 'do it better' play, not blue ocean.</t>
         </is>
       </c>
     </row>
@@ -1247,17 +1226,17 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Wood-burning stove spares: glass cut to model, rope, fire bricks</t>
+          <t>Blind spare parts by system &amp; brand</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B/A</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>UK glass processors cut to size; rope/bricks from UK importers. The classic supplier-backed play.</t>
+          <t>UK component wholesalers (Louvolite/Decora) or AliExpress; chains, brackets, wands.</t>
         </is>
       </c>
       <c r="E9" s="13" t="n">
@@ -1270,10 +1249,10 @@
         <v>2</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J9" s="13" t="n">
         <v>4</v>
@@ -1288,12 +1267,12 @@
       </c>
       <c r="M9" s="13" t="inlineStr">
         <is>
-          <t>Validated (GB+US)</t>
+          <t>Validated (GB+US + SERP) — DOWNGRADED v2</t>
         </is>
       </c>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>Solid aggregate GB demand ~950/mo (stove rope 500, stove glass 200, fire bricks 150, replacement stove glass 100), KD≈0, and it's consumable. CAPPED: five+ formalised specialists already rank (stoveglassreplacement.co.uk, ukglasscentre, fastglassdirect…). Only viable via an unserved sub-angle, e.g. a true stove-brand × model matrix.</t>
+          <t>Demand solid (~700/mo cluster; #1 page TP ~1,400) but Joe's live check is right: blindspares.co.uk, blindspartsdirect.co.uk and blindparts.co.uk all sit on page 1 — three named specialists. Occupied, however dated. Capped.</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1282,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Watch straps, spring bars &amp; tools by lug width / model</t>
+          <t>Derailleur hangers &amp; model-specific bike smallparts</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1313,14 +1292,14 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>AliExpress; NATO/FKM/leather × 18–24mm × model-fit pages. Letter-post.</t>
+          <t>Hanger-by-frame-model; the canonical matrix product.</t>
         </is>
       </c>
       <c r="E10" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>2</v>
@@ -1332,10 +1311,10 @@
         <v>3</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L10" s="13" t="inlineStr">
         <is>
@@ -1344,68 +1323,68 @@
       </c>
       <c r="M10" s="13" t="inlineStr">
         <is>
-          <t>Inferred</t>
+          <t>Validated (GB+US + SERP)</t>
         </is>
       </c>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>Big enthusiast demand and perfect postage economics. CAPPED: WatchGecko, Barton, StrapsCo et al are formalised. Sub-niches (model-specific fitted rubber, vintage) may still be open — needs its own SERP pass.</t>
+          <t>Biggest matrix demand found (GB 1,500, US 2,900) but rearmechhanger.com owns positions 1-2. Late entry only with an angle.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Golf trolley spares &amp; batteries (PowaKaddy / Motocaddy)</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>A/B</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Wheels, clips, chargers by model; batteries via UK battery wholesaler (drop-ship).</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="n">
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Wood-burning stove spares (glass cut to model, rope, bricks)</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>UK glass processors; supplier-backed consumables.</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="H11" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="I11" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="L11" s="10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>Validated (partial)</t>
-        </is>
-      </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>golf trolley battery 250/mo KD0; powakaddy spares 50. The ranking specialist electricgolftrolleyspares.com (pos 7) is visibly ropey — outrank or acquire. Adjacent to the proven golf-weights audience. Battery logistics (weight, lithium rules) cap the economics score.</t>
+      <c r="J11" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>B (capped)</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="inlineStr">
+        <is>
+          <t>Validated (GB+US + SERP)</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>~950/mo cluster, KD≈0, consumable — but five formalised specialists rank. Sub-angle (true stove-brand × model matrix) or nothing.</t>
         </is>
       </c>
     </row>
@@ -1415,21 +1394,21 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Espresso machine spares &amp; accessories (Gaggia / Sage / DeLonghi)</t>
+          <t>Watch straps, spring bars &amp; tools by lug width / model</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>A/B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>AliExpress accessories + UK parts distributors; baskets, gaskets, tampers by machine model.</t>
+          <t>AliExpress; NATO/FKM/leather × lug width × model-fit.</t>
         </is>
       </c>
       <c r="E12" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" s="13" t="n">
         <v>4</v>
@@ -1438,198 +1417,198 @@
         <v>2</v>
       </c>
       <c r="H12" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <t>B (capped)</t>
+        </is>
+      </c>
+      <c r="M12" s="13" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>WatchGecko et al formalised. Sub-niches may be open; needs live check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Espresso machine spares &amp; accessories by machine model</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>A/B</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Baskets, gaskets, tampers by model; UK parts distributors.</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="G13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="J12" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K12" s="13" t="n">
+      <c r="J13" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="L12" s="13" t="inlineStr">
+      <c r="L13" s="13" t="inlineStr">
         <is>
           <t>B (capped)</t>
         </is>
       </c>
-      <c r="M12" s="13" t="inlineStr">
-        <is>
-          <t>Validated (GB+US)</t>
-        </is>
-      </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>gaggia classic parts 70 GB/150 US, delonghi spare parts 250, portafilter basket 250 GB/900 US; consumable gaskets/filters. CAPPED: mrbean2cup, Shades of Coffee, Gaggia Direct already serve it competently. Home-barista boom keeps it interesting if a gap appears at machine-model level.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Trailer parts — Ifor Williams, Erde, Franc (lights, couplings, boards)</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="M13" s="13" t="inlineStr">
+        <is>
+          <t>Validated (GB+US + SERP)</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>mrbean2cup / Shades of Coffee serve it competently. Watch for machine-model-level gaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Made-to-measure netting (garden, fruit cage, golf, cargo, sports)</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Partner with a regional trailer dealer holding stock; you own the search front-end.</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="n">
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>UK net loft partner; dimension × mesh × sport matrix.</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="G14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G13" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" s="10" t="n">
+      <c r="K14" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="L14" s="13" t="inlineStr">
+        <is>
+          <t>B (capped)</t>
+        </is>
+      </c>
+      <c r="M14" s="13" t="inlineStr">
+        <is>
+          <t>Validated (GB pulls + LIVE SERP) — NEW v2</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>Demand is enormous and easy (golf net 5,600 KD0, garden netting 2,300, cargo net 1,600, fruit cage 1,200, bird netting 1,000, pond netting 700 — all KD 0-3). But live SERP: Huck Nets, Henry Cowls, nets4you, Net World Sports, Cocus all sell bespoke netting. Occupied at both consumer and MTM level. Capped — only enterable via an unserved sub-vertical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Cricket &amp; sports ground equipment (covers, sight screens, boundary ropes)</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Canvas/PVC fabricator partner; £2k-£10k tickets to clubs/schools/councils.</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="L13" s="10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>Validated (GB)</t>
-        </is>
-      </c>
-      <c r="N13" s="8" t="inlineStr">
-        <is>
-          <t>ifor williams parts 700/mo GB KD0 (UK-only term, US=0). SERP = OEM distributor page + fragmented regional dealers with weak sites + eBay. The blocker is freight: many parts are heavy/awkward → parcels/pallets, killing the letter-post economics. Works as archetype B with a dealer fulfilling.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Trampoline spares by brand &amp; size (springs, nets, pads, poles)</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>AliExpress; matrix = brand × diameter × part. Nets/pads degrade in UK weather.</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="L14" s="10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="M14" s="10" t="inlineStr">
-        <is>
-          <t>Inferred</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t>Strong repeat dynamics and clear matrix; bulky items hurt postage economics. eBay-churn competition. Worth a validation pass in spring.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Pushchair / pram wheels &amp; spares by model</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>AliExpress; wheels, tyres, clips by model (Bugaboo/Silver Cross/iCandy…). Distress purchase.</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="L15" s="10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="M15" s="10" t="inlineStr">
-        <is>
-          <t>Inferred</t>
-        </is>
-      </c>
-      <c r="N15" s="8" t="inlineStr">
-        <is>
-          <t>High-intent distress purchases, eBay churn competition, decent matrix. One-off purchases (kids outgrow) and some liability sensitivity.</t>
+      <c r="H15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="L15" s="13" t="inlineStr">
+        <is>
+          <t>B (capped)</t>
+        </is>
+      </c>
+      <c r="M15" s="13" t="inlineStr">
+        <is>
+          <t>Validated (GB pulls + LIVE SERP) — NEW v2</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Real high-value demand: cricket covers 300/mo @ $4.50 CPC (!), sight screens ~600/mo combined, scoreboards family ~1,500/mo mixed. But live SERP shows 5+ specialists (3D Sports, total-play, Durant, ACS, Stuart Canvas, Matchsaver). Occupied. NOTE: 'cricket pitch protection covers {city}' ×10 keyword family is AI-synthetic noise — real demand is smaller than raw Ahrefs suggests. Capped.</t>
         </is>
       </c>
     </row>
@@ -1639,39 +1618,39 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Aquarium filter impellers, media &amp; spares by filter model</t>
+          <t>LED / electronic scoreboards (multi-sport)</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>AliExpress; fits Fluval/Eheim/Oase × filter model. Letter-post. Consumable media.</t>
+          <t>LED assembler or signmaker partner; £1k-£8k tickets to clubs/schools.</t>
         </is>
       </c>
       <c r="E16" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="10" t="n">
         <v>3</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>3</v>
       </c>
       <c r="K16" s="10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
@@ -1680,12 +1659,12 @@
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>Validated (weak)</t>
+          <t>Partially validated — validate next</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>GB terms thin (fluval impeller 10, filter media 150; eheim spares 10) — demand is real but small and partly on eBay/Amazon. Keep as a bolt-on candidate rather than a lead site.</t>
+          <t>cricket scoreboard 1,000/mo (mixed intent) + led/electronic/portable/digital variants ~550/mo + led scoreboard 150. Not live-checked; scoreboard SERPs likely mix info + retailers. Worth one live pass.</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1674,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Awning &amp; gazebo spares by model (poles, connectors, feet)</t>
+          <t>Trampoline spares by brand &amp; size</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1705,23 +1684,23 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>AliExpress + UK leisure trade; matrix by brand/model. Seasonal.</t>
+          <t>Springs, nets, pads; degrade in UK weather.</t>
         </is>
       </c>
       <c r="E17" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>4</v>
       </c>
       <c r="G17" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" s="10" t="n">
-        <v>3</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>3</v>
@@ -1741,7 +1720,7 @@
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>Caravan-adjacent audience, eBay churn competition, but strongly seasonal and part-identification is hard for customers (returns risk).</t>
+          <t>Repeat purchase + matrix; bulky. Validate in spring.</t>
         </is>
       </c>
     </row>
@@ -1751,39 +1730,39 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Robot mower blades &amp; spares by model</t>
+          <t>Golf trolley spares &amp; batteries</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A/B</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>AliExpress; blades by model (Husqvarna/Worx/Gardena…). Consumable. Letter-post.</t>
+          <t>Wheels, clips, chargers by model; battery via UK wholesaler.</t>
         </is>
       </c>
       <c r="E18" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="10" t="n">
         <v>4</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K18" s="10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
@@ -1792,12 +1771,12 @@
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>Validated (weak) — watchlist</t>
+          <t>Validated (partial)</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>Today's GB demand is small (robot mower blades 50/mo) but the installed base compounds every year — a deliberate get-in-early bet. Revisit annually.</t>
+          <t>electricgolftrolleyspares.com (pos 7) visibly ropey. Battery logistics cap it.</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1786,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Snooker &amp; pool cue tips, ferrules &amp; accessories</t>
+          <t>Pushchair / pram wheels &amp; spares by model</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -1817,379 +1796,379 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>AliExpress; tips by diameter/hardness. Letter-post perfect.</t>
+          <t>Distress purchase; eBay churn.</t>
         </is>
       </c>
       <c r="E19" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H19" s="10" t="n">
+      <c r="J19" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="L19" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t>Decent matrix; one-off purchases; liability care.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Padel &amp; pickleball club equipment/consumables layer</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Not courts/canopies (taken) — the consumables under them: replacement nets, court maintenance, branded club gear.</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>Partially validated — watchlist</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t>Padel construction/canopy layer already colonised (8 specialists live-checked: Fordingbridge, Padeltech, Portico…) and even that is only 350+150/mo. Accessory demand nascent (padel court equipment 40/mo; pickleball net 500/mo KD0 is the one real term). The lesson: new-sport gold rushes colonise fast; watch the consumables layer as the installed base grows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Aquarium filter impellers &amp; media by model</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Fits Fluval/Eheim × model; consumable media.</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>Validated (weak)</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>Real but small; bolt-on candidate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Awning &amp; gazebo spares by model</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Poles, connectors, feet; caravan-adjacent.</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t>Seasonal; part-identification returns risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Snooker / pool cue tips &amp; ferrules</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Tips by diameter/hardness; letter-post.</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I19" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" s="10" t="n">
+      <c r="I23" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="K19" s="10" t="n">
+      <c r="K23" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="L19" s="10" t="inlineStr">
+      <c r="L23" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M19" s="10" t="inlineStr">
+      <c r="M23" s="10" t="inlineStr">
         <is>
           <t>Inferred</t>
         </is>
       </c>
-      <c r="N19" s="8" t="inlineStr">
-        <is>
-          <t>Great postage economics, loyal hobbyists; matrix is shallower (diameter, not brand×model) and demand modest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="N23" s="8" t="inlineStr">
+        <is>
+          <t>Shallow matrix, modest demand, great postage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Robot mower blades &amp; spares by model</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Blades by model; consumable; letter-post.</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>Validated (weak) — watchlist</t>
+        </is>
+      </c>
+      <c r="N24" s="8" t="inlineStr">
+        <is>
+          <t>Installed base compounds; revisit annually.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Chainsaw chains &amp; bars by machine model</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>AliExpress/Oregon-compatible; chain-by-model matrix. Consumable.</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="13" t="n">
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Chain-by-model; consumable.</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="G25" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H20" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I20" s="13" t="n">
+      <c r="H25" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="J20" s="13" t="n">
+      <c r="J25" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K20" s="13" t="n">
+      <c r="K25" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="L20" s="13" t="inlineStr">
+      <c r="L25" s="13" t="inlineStr">
         <is>
           <t>B (capped)</t>
         </is>
       </c>
-      <c r="M20" s="13" t="inlineStr">
+      <c r="M25" s="13" t="inlineStr">
         <is>
           <t>Inferred</t>
         </is>
       </c>
-      <c r="N20" s="11" t="inlineStr">
-        <is>
-          <t>Real matrix + consumable, CAPPED: Amazon and established forestry retailers own these SERPs; safety-liability angle on no-name chains.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>Guitar &amp; bass parts by model (pickguards, saddles, knobs, tuners)</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>AliExpress; fits Strat/Tele/LP × part. Letter-post.</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="I21" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K21" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="L21" s="13" t="inlineStr">
-        <is>
-          <t>C (capped)</t>
-        </is>
-      </c>
-      <c r="M21" s="13" t="inlineStr">
-        <is>
-          <t>Inferred</t>
-        </is>
-      </c>
-      <c r="N21" s="11" t="inlineStr">
-        <is>
-          <t>Lovely matrix and postage, CAPPED: Northwest Guitars and others are formalised UK specialists; one-off purchases.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>Airgun magazines, fill probes &amp; adapters by model</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>Matrix by rifle model; letter-post. UK legal for airguns but age-verification friction.</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="I22" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="L22" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M22" s="16" t="inlineStr">
-        <is>
-          <t>Inferred</t>
-        </is>
-      </c>
-      <c r="N22" s="14" t="inlineStr">
-        <is>
-          <t>Enthusiast niche with real matrix; Best Fittings already semi-formalised; compliance friction (age checks, couriers) drags economics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>Fishing reel spares &amp; spare spools by model</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>AliExpress + brand service parts; spool-by-reel-model matrix.</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="G23" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="I23" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="L23" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M23" s="16" t="inlineStr">
-        <is>
-          <t>Validated (weak)</t>
-        </is>
-      </c>
-      <c r="N23" s="14" t="inlineStr">
-        <is>
-          <t>Ahrefs shows almost nothing (10–20/mo) — this demand lives inside eBay search, not Google. A marketplace play, not an SEO site.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Lawnmower &amp; garden machinery spares by model</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>UK wholesaler partner; blades/belts/filters by model.</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F24" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G24" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="L24" s="13" t="inlineStr">
-        <is>
-          <t>C (capped)</t>
-        </is>
-      </c>
-      <c r="M24" s="13" t="inlineStr">
-        <is>
-          <t>Inferred</t>
-        </is>
-      </c>
-      <c r="N24" s="11" t="inlineStr">
-        <is>
-          <t>CAPPED: eSpares/Amazon pressure + established mower-spares sites; heavy items. The Calda-Morley-style XDV belt line is the interesting corner.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>Kayak / SUP fins &amp; fittings by brand</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>AliExpress; US Box/slide-in fins by brand. Light.</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="G25" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="H25" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="I25" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" s="16" t="n">
-        <v>17</v>
-      </c>
-      <c r="L25" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M25" s="16" t="inlineStr">
-        <is>
-          <t>Inferred</t>
-        </is>
-      </c>
-      <c r="N25" s="14" t="inlineStr">
-        <is>
-          <t>Growing sport but thin measurable demand; seasonal; matrix moderate.</t>
+      <c r="N25" s="11" t="inlineStr">
+        <is>
+          <t>Amazon + forestry retailers own it; liability angle.</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2178,7 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Bearings by designation — the Calda Morley play</t>
+          <t>Power transmission belts &amp; taper-lock by code — the Calda Morley play</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
@@ -2209,7 +2188,7 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Front-end for a trade distributor (e.g. Calda-Morley: bearings, belts, chain, seals on a brochure site).</t>
+          <t>V/wedge/poly-v belts by section×length; taper lock bushes by bore.</t>
         </is>
       </c>
       <c r="E26" s="13" t="n">
@@ -2240,12 +2219,12 @@
       </c>
       <c r="M26" s="13" t="inlineStr">
         <is>
-          <t>Inferred</t>
+          <t>Validated (GB pull + LIVE SERP) — CLOSED v2</t>
         </is>
       </c>
       <c r="N26" s="11" t="inlineStr">
         <is>
-          <t>The supplier and matrix are perfect (6204-2RS etc.), CAPPED: Simply Bearings and Bearing Boys are exactly this idea, executed years ago, with huge catalogues. Illustrative of archetype B rather than an open opportunity.</t>
+          <t>The spec long-tail is real (~2,500/mo denoised: v belt 1,000, poly v 350, taper lock family ~700) but the live SERP is wall-to-wall formalised distributors: Bearing Boys, Simply Bearings, Acorn, George Lodge, TransDev, Bearing Station. The Calda-Morley category is already online — the generalisable lesson is to find its equivalent in trades that AREN'T (scan method in Read Me).</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2234,7 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Appliance door seals, hinges &amp; handles by model</t>
+          <t>Equestrian arena mirrors &amp; arena equipment</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -2265,14 +2244,14 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>UK spares wholesalers; oven/fridge/washing machine model matrix.</t>
+          <t>Mirror fabricator partner; £1k-£3k tickets.</t>
         </is>
       </c>
       <c r="E27" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G27" s="13" t="n">
         <v>1</v>
@@ -2281,13 +2260,13 @@
         <v>3</v>
       </c>
       <c r="I27" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J27" s="13" t="n">
         <v>3</v>
       </c>
       <c r="K27" s="13" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L27" s="13" t="inlineStr">
         <is>
@@ -2296,68 +2275,68 @@
       </c>
       <c r="M27" s="13" t="inlineStr">
         <is>
-          <t>Inferred</t>
+          <t>Validated (GB pull + LIVE SERP) — CLOSED v2</t>
         </is>
       </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>Massive matrix, CAPPED: eSpares/Ransom Spares own this comprehensively. No entry.</t>
+          <t>Shockingly colonised for a micro-niche: SIX dedicated specialists live on page 1 (made2measure, mirrors4riding, arenamirrors.com, equestrianreflections, arenamirrorsplus, simplyarenamirrors) for 150/mo. Proof that high-ticket rural niches are not automatically empty. Arena letters/harrows similar.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>Sash window &amp; period-property ironmongery</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Changing room benches &amp; locker-room fit-out</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>UK foundry/wholesaler partner; pulleys, fasteners, restrictors.</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="n">
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>UK joinery partner; schools/gyms/clubs.</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="G28" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H28" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="I28" s="16" t="n">
+      <c r="H28" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K28" s="16" t="n">
+      <c r="J28" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="L28" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M28" s="16" t="inlineStr">
-        <is>
-          <t>Inferred</t>
-        </is>
-      </c>
-      <c r="N28" s="14" t="inlineStr">
-        <is>
-          <t>Charming niche, weak matrix (no brand×model), modest demand, one-off purchases.</t>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>C (capped)</t>
+        </is>
+      </c>
+      <c r="M28" s="13" t="inlineStr">
+        <is>
+          <t>Validated (GB + LIVE SERP) — CLOSED v2</t>
+        </is>
+      </c>
+      <c r="N28" s="11" t="inlineStr">
+        <is>
+          <t>600/mo KD0 @ $1.40 CPC looked juicy, but the live SERP is workplace-catalogue giants (AJ Products, Slingsby, BiGDUG, Commercial Washrooms). Occupied.</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2346,7 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Heritage cast iron — staddle stones, guttering, radiator feet (shepherd-hut-wheels pattern)</t>
+          <t>Commercial gym equipment spares (cables, pads, upholstery by machine)</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
@@ -2377,53 +2356,2778 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>UK foundry partner ships freight; you own search + brand.</t>
+          <t>UK upholsterer + cable maker; gyms pay well.</t>
         </is>
       </c>
       <c r="E29" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="L29" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>Validated (weak) — KILLED v2</t>
+        </is>
+      </c>
+      <c r="N29" s="14" t="inlineStr">
+        <is>
+          <t>The matching-terms pull exposed it: 'gym cable' demand is people BUYING cable machines, not spares. Real spares terms tiny (gym equipment parts 100, treadmill belt 100). No search market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Guitar &amp; bass parts by model</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Pickguards, saddles by model.</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="H30" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I30" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="16" t="n">
+      <c r="J30" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="H29" s="16" t="n">
+      <c r="K30" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="L30" s="13" t="inlineStr">
+        <is>
+          <t>C (capped)</t>
+        </is>
+      </c>
+      <c r="M30" s="13" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="N30" s="11" t="inlineStr">
+        <is>
+          <t>Northwest Guitars et al formalised.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Airgun magazines, fill probes &amp; adapters by model</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>Matrix by rifle model.</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I31" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="L31" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="N31" s="14" t="inlineStr">
+        <is>
+          <t>Best Fittings semi-formalised; compliance friction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Fishing reel spares &amp; spools</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>Spool-by-reel matrix.</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="16" t="n">
+      <c r="F32" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G32" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I32" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="L32" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>Validated (weak)</t>
+        </is>
+      </c>
+      <c r="N32" s="14" t="inlineStr">
+        <is>
+          <t>Demand lives on eBay, not Google.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Lawnmower &amp; garden machinery spares by model</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Blades/belts/filters.</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="L33" s="13" t="inlineStr">
+        <is>
+          <t>C (capped)</t>
+        </is>
+      </c>
+      <c r="M33" s="13" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="N33" s="11" t="inlineStr">
+        <is>
+          <t>eSpares/Amazon pressure; heavy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Kayak / SUP fins &amp; fittings</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>Fins by brand.</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="16" t="n">
+      <c r="F34" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="16" t="n">
+      <c r="J34" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="L34" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="N34" s="14" t="inlineStr">
+        <is>
+          <t>Thin demand, seasonal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Appliance door seals &amp; hinges by model</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Oven/fridge/washer matrix.</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="L35" s="13" t="inlineStr">
+        <is>
+          <t>C (capped)</t>
+        </is>
+      </c>
+      <c r="M35" s="13" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="N35" s="11" t="inlineStr">
+        <is>
+          <t>eSpares owns comprehensively.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>Sash window &amp; period ironmongery</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>Pulleys, fasteners.</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="L36" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="N36" s="14" t="inlineStr">
+        <is>
+          <t>Weak matrix, one-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>Heritage cast iron (staddle stones, guttering, rad feet)</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>Foundry partner, freight.</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="L29" s="16" t="inlineStr">
+      <c r="L37" s="16" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M29" s="16" t="inlineStr">
+      <c r="M37" s="16" t="inlineStr">
         <is>
           <t>Inferred</t>
         </is>
       </c>
-      <c r="N29" s="14" t="inlineStr">
-        <is>
-          <t>The shepherd-hut-wheels shape: tiny volume, very high ticket. Fails the postage/matrix criteria but could work as a high-ticket archetype-B side bet if the foundry relationship lands.</t>
+      <c r="N37" s="14" t="inlineStr">
+        <is>
+          <t>Shepherd-hut-wheels shape; high ticket offsets, capital heavy.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N29"/>
+  <autoFilter ref="A1:N37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Angle</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Keyword (GB)</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Volume /mo</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>CPC (USD)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Branded sports matting</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>commercial gym flooring</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="n">
+        <v>500</v>
+      </c>
+      <c r="D2" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>Real — the funnel head term</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Branded sports matting</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>commercial gym flooring uk</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="n">
+        <v>200</v>
+      </c>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Branded sports matting</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>custom yoga mats</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Real — print-on-mat demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Branded sports matting</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>commercial gym mats</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Branded sports matting</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>boxing ring canvas</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Real — printable canvas</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Branded sports matting</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>weightlifting platform</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Real — logo-inlay adjacent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Branded sports matting</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>branded yoga mats</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Branded sports matting</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>personalised yoga mats uk</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Branded sports matting</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>commercial gym floor mats</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>Real — note $3.00 CPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Branded sports matting</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>personalised yoga mats</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>80</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Branded sports matting</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>branded yoga mats uk</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>80</v>
+      </c>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>Branded sports matting</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>custom rubber gym flooring</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="D13" s="19" t="n"/>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>CAUTION — part of AI-synthetic 'custom/bespoke X gym flooring' fan-out family</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Branded sports matting</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>bespoke commercial gym flooring</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>CAUTION — synthetic family</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Branded sports matting</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>custom brass gym flooring</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>70</v>
+      </c>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="20" t="n"/>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>SYNTHETIC — impossible product; proves the fan-out family is AI noise</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Branded sports matting</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>custom wrestling mats</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>Zero volume — nobody searches what nobody sells; demand expressed via generic terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Branded sports matting</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>branded gym flooring</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>Zero volume — same</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Cricket ground equipment</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>cricket scoreboard</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>Real but mixed intent (live scores vs product)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Cricket ground equipment</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>cricket covers</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>Real — $4.50 CPC = serious commercial value</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Cricket ground equipment</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>cricket sight screen (+3 variants)</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>640</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>Real — combined variants</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Cricket ground equipment</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>cricket batting cage</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>200</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Cricket ground equipment</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>mobile cricket covers</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Cricket ground equipment</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>cricket boundary rope</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>Real (see Southern Ropes memory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Cricket ground equipment</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>digital/electronic/led/portable cricket scoreboard</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="n">
+        <v>550</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>Real — combined product-intent variants</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Cricket ground equipment</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>cricket netting</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Cricket ground equipment</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>flat sheet cricket covers</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>Cricket ground equipment</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>cricket pitch covers</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>Cricket ground equipment</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>artificial cricket pitch</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>Cricket ground equipment</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>cricket ball stop netting</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>80</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>Cricket ground equipment</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>cricket pitch protection covers {london/manchester/derby/… ×10}</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="n">
+        <v>850</v>
+      </c>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="20" t="n"/>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>SYNTHETIC — AI-assistant city fan-out; do NOT count toward demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Made-to-measure netting</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>golf net</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>5600</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>Real — consumer, Amazon-leaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>Made-to-measure netting</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>golf practice net</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="n">
+        <v>2600</v>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>Made-to-measure netting</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>garden netting</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>Made-to-measure netting</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>cargo net</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>Made-to-measure netting</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>fruit cage</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>Made-to-measure netting</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>golf net for garden</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>Made-to-measure netting</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>bird netting</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D37" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>Made-to-measure netting</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>pond netting</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="n">
+        <v>700</v>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Made-to-measure netting</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>garden mesh netting</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="n">
+        <v>600</v>
+      </c>
+      <c r="D39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Made-to-measure netting</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>golf chipping net</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="D40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>Made-to-measure netting</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>fruit cage netting</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>400</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>Made-to-measure netting</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>sports netting</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="n">
+        <v>350</v>
+      </c>
+      <c r="D42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>Made-to-measure netting</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>anti bird netting</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>Made-to-measure netting</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>walk in fruit cage</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="n">
+        <v>200</v>
+      </c>
+      <c r="D44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>Made-to-measure netting</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>cat netting for garden</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="n">
+        <v>200</v>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>PT belts &amp; taper lock</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>v belt</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>PT belts &amp; taper lock</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>poly v belt</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="n">
+        <v>350</v>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>PT belts &amp; taper lock</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>taper lock</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>PT belts &amp; taper lock</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>v belt pulley</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D49" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>PT belts &amp; taper lock</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>taper lock bush</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>PT belts &amp; taper lock</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>vee belt</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="n">
+        <v>200</v>
+      </c>
+      <c r="D51" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>PT belts &amp; taper lock</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>wedge belt</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>PT belts &amp; taper lock</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>spz</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D53" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>Real (section code)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>PT belts &amp; taper lock</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>v belt size chart</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D54" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>Real — informational asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>PT belts &amp; taper lock</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>htd belt</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="D55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>PT belts &amp; taper lock</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>spz belts</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="n">
+        <v>70</v>
+      </c>
+      <c r="D56" s="16" t="n"/>
+      <c r="E56" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>PT belts &amp; taper lock</t>
+        </is>
+      </c>
+      <c r="B57" s="18" t="inlineStr">
+        <is>
+          <t>seiko spb / spb-tours / adria 600 spb / ancon spb</t>
+        </is>
+      </c>
+      <c r="C57" s="19" t="n">
+        <v>640</v>
+      </c>
+      <c r="D57" s="19" t="n"/>
+      <c r="E57" s="20" t="n"/>
+      <c r="F57" s="18" t="inlineStr">
+        <is>
+          <t>HOMONYM NOISE — watches, tours, campervans, wall ties; excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>Equestrian arena</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>horse arena</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="n">
+        <v>350</v>
+      </c>
+      <c r="D58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>Real — construction-leaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>Equestrian arena</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>horse menage</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="D59" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>Equestrian arena</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>horse walker</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="n">
+        <v>200</v>
+      </c>
+      <c r="D60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>Real — high ticket</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>Equestrian arena</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>arena mirrors</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D61" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
+          <t>Real — but 6 specialists live</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>Equestrian arena</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>arena harrow</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>Equestrian arena</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>equestrian arena</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>Real — $1.20 CPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>Equestrian arena</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>horse arena equipment</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D64" s="16" t="n"/>
+      <c r="E64" s="17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>Equestrian arena</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>horse arena letters</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="D65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
+        <is>
+          <t>Real — small product niche</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>Equestrian arena</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>lunge pen</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="D66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="18" t="inlineStr">
+        <is>
+          <t>Equestrian arena</t>
+        </is>
+      </c>
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>equestrian arena/menage covers (+near me variants)</t>
+        </is>
+      </c>
+      <c r="C67" s="19" t="n">
+        <v>340</v>
+      </c>
+      <c r="D67" s="19" t="n"/>
+      <c r="E67" s="20" t="n"/>
+      <c r="F67" s="18" t="inlineStr">
+        <is>
+          <t>CAUTION — likely synthetic fan-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>Equestrian arena</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>menage / menage a trois family</t>
+        </is>
+      </c>
+      <c r="C68" s="19" t="n">
+        <v>2600</v>
+      </c>
+      <c r="D68" s="19" t="n"/>
+      <c r="E68" s="20" t="n"/>
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>HOMONYM NOISE — excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>Gym equipment spares</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>cable machine home gym / gym cable machine family</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D69" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>WRONG INTENT — buying machines, not spares; killed the idea</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>Gym equipment spares</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>gym cable attachments</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="n">
+        <v>200</v>
+      </c>
+      <c r="D70" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>Real — accessory, not spares</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>Gym equipment spares</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>gym equipment parts</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D71" s="16" t="n"/>
+      <c r="E71" s="17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F71" s="14" t="inlineStr">
+        <is>
+          <t>Real but tiny</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>Gym equipment spares</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>treadmill belt</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F72" s="14" t="inlineStr">
+        <is>
+          <t>Real but tiny</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>Gym equipment spares</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>treadmill parts</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="n">
+        <v>70</v>
+      </c>
+      <c r="D73" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F73" s="14" t="inlineStr">
+        <is>
+          <t>Real but tiny</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="14" t="inlineStr">
+        <is>
+          <t>Padel &amp; emerging sports</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>padel court construction</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="n">
+        <v>350</v>
+      </c>
+      <c r="D74" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F74" s="14" t="inlineStr">
+        <is>
+          <t>Real — installer/construction intent</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>Padel &amp; emerging sports</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>pickleball net</t>
+        </is>
+      </c>
+      <c r="C75" s="16" t="n">
+        <v>500</v>
+      </c>
+      <c r="D75" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>Real — the one open-ish product term</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>Padel &amp; emerging sports</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>padel court canopy</t>
+        </is>
+      </c>
+      <c r="C76" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D76" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>Real — 8 specialists live</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="14" t="inlineStr">
+        <is>
+          <t>Padel &amp; emerging sports</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>padel court cover</t>
+        </is>
+      </c>
+      <c r="C77" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D77" s="16" t="n"/>
+      <c r="E77" s="17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>Padel &amp; emerging sports</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>padel court maintenance</t>
+        </is>
+      </c>
+      <c r="C78" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="D78" s="16" t="n"/>
+      <c r="E78" s="17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>Real — nascent</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>Padel &amp; emerging sports</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>padel court equipment</t>
+        </is>
+      </c>
+      <c r="C79" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="D79" s="16" t="n"/>
+      <c r="E79" s="17" t="n"/>
+      <c r="F79" s="14" t="inlineStr">
+        <is>
+          <t>Real — nascent</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>Facility fit-out</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>changing room benches</t>
+        </is>
+      </c>
+      <c r="C80" s="16" t="n">
+        <v>600</v>
+      </c>
+      <c r="D80" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F80" s="14" t="inlineStr">
+        <is>
+          <t>Real — but catalogue giants own the SERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>Facility fit-out</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>led scoreboard</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D81" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F81" s="14" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F81"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Query (Google UK, live, Aug 2026)</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Dedicated specialists on page 1</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Who's actually there</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>branded gym mats / gym mats with logo</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>0 true specialists</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>Generic gym-flooring shops (Gym Revolution, Mirafit, gym-flooring.com), entrance DOORMAT printers (First Mats, UK Mats Direct, Slip-Not), eBay, a US facility-branding site (Enhance Mats), epicmats.co.uk's logo-mat category (nearest thing).</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>MIS-SERVED — Google substitutes doormats because no printed-sports-mat specialist exists. This is the golf-weights-shaped gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>cricket pitch covers</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>3D Sports, total-play, Durant Cricket, ACS, Matchsaver, Stuart Canvas, Net World Sports.</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>OCCUPIED — formalised ground-equipment field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>netting made to measure</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Henry Cowls, Huck Nets, nets4you, Net World Sports custom netting, Cocus, safetynet365, W M James.</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>OCCUPIED at both consumer and bespoke level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>vee belts</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Bearing Boys, George Lodge, TransDev, Simply Bearings, Acorn Industrial, Medway PT, Bearing Station, Bearings R Us.</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>OCCUPIED — the Calda-Morley category is already online.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>horse arena mirrors</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>made2measure, mirrors4riding, arenamirrors.com, equestrianreflections, arenamirrorsplus, simplyarenamirrors.</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>OCCUPIED — six specialists for 150 searches/mo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>changing room benches</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>0 specialists, but…</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Workplace-catalogue giants: Commercial Washrooms, AJ Products, Slingsby, BiGDUG, Simply Lockers, Venesta, Continental Sports.</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>OCCUPIED by generalist catalogues with big ranges — worse than specialists to displace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>padel court canopy</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Fordingbridge, Padeltech, A&amp;S Landscape, Portico Sport, Rocklyn, Kit Buildings, SG Padel, Aloteks.</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>OCCUPIED — new-sport layers colonise fast; watch the consumables layer instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>v1 Ahrefs-cached SERP checks (hot tub filters, ear pads, blinds, Ifor Williams, stove, derailleur, golf trolley, gaggia) are retained in the v1 commit history; their verdicts are folded into Scorecard v2 notes.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4674,250 +7378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Keyword (GB)</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>GB vol /mo</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Who owns the top 10</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>hot tub filters</t>
-        </is>
-      </c>
-      <c r="B2" s="14" t="n">
-        <v>1100</v>
-      </c>
-      <c r="C2" s="14" t="inlineStr">
-        <is>
-          <t>Hot-tub dealers' afterthought category pages (Outdoor Living, Happy Hot Tubs, Wave Spas, Castle, HotSpring) + eBay + a YouTube video. No dedicated filter specialist.</t>
-        </is>
-      </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>WINNABLE — no specialist; consumable demand unowned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>replacement ear pads</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="n">
-        <v>40</v>
-      </c>
-      <c r="C3" s="14" t="inlineStr">
-        <is>
-          <t>wickedcushions.com (US specialist) #1, then UK generalists: Headset Store, Lindy, Amazon, Sennheiser OEM, a silent-disco shop.</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
-        <is>
-          <t>WINNABLE — no UK model-matrix specialist; the US #1 proves the model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>blind spare parts</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="n">
-        <v>150</v>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>Five+ small specialists splitting the demand: Blinds By Post, Direct Order Blinds, blindspares.co.uk, blindspartsdirect.co.uk, blindparts.co.uk (.asp-era site), verticalblindsparts.co.uk + Amazon.</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>WINNABLE — fragmented, dated competition; consolidate the intent on one modern site.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>vertical blind parts</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="n">
-        <v>350</v>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>Amazon #1, then verticalblindsparts.co.uk and assorted dated UK/US micro-sites (US sites ranking in GB = weak local competition signal).</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>WINNABLE — same fragmented field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>ifor williams parts</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="n">
-        <v>700</v>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>OEM (iwt.co.uk) top, then regional trailer dealers with weak sites (Barlow, TrailerTek, Edwards, Western Towing) + an eBay store.</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>WINNABLE as archetype B with a dealer partner — but freight economics are the real constraint.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>golf trolley battery</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Battery retailers (GoBatteries, Alpha, AllBatteries), Motocaddy OEM, and the visibly ropey specialist electricgolftrolleyspares.com at position 7.</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>PARTLY WINNABLE — the specialist slot is weakly held; battery logistics cap the prize.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>gaggia classic parts</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Competent UK specialists: Mr Bean2Cup, Shades of Coffee, Gaggia Direct, plus forums/diagrams (Reddit, Scribd).</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>SERVED — enter only if a machine-model-matrix gap shows up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>stove glass</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n">
-        <v>200</v>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Five formalised specialists: stoveglassreplacement.co.uk, UK Glass Centre, Stove Supermarket, Fast Glass Direct, Glowing Embers, Stove Glass Shop.</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>SERVED — crowded with exactly this business model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>stove rope</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Fragmented stove shops + HETAS/OEM guides; Stove Wizard the nearest specialist. Softer field than stove glass.</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>PARTLY WINNABLE — but only as part of a wider stove-consumables play.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>derailleur hanger</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>rearmechhanger.com holds #1 AND #2, plus Halfords, Mountain Bike Components, content (BikeRadar, YouTube, Reddit).</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>TAKEN — the niche's golf-weights already exists. Proof of model, late entry.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D11"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5047,14 +7508,14 @@
       <c r="F4" s="14" t="n"/>
       <c r="G4" s="14" t="inlineStr">
         <is>
-          <t>Wakefield bearings/transmission distributor: deep spec-matrix catalogue (bearings by designation, belts, chain, seals) on a brochure site with a phone number. The kind of supplier a front-end gets built for — though in bearings specifically, Simply Bearings/Bearing Boys already did it.</t>
+          <t>Wakefield bearings/transmission distributor: deep spec-matrix catalogue on a brochure site. The kind of supplier a front-end gets built for — but v2's live check shows the bearings/belts CATEGORY is already online (Simply Bearings, Bearing Boys). Find its equivalent in a trade that isn't.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>Source: Ahrefs site-explorer-metrics, mode=subdomains, GB, 2026-08-01. Traffic value converted from USD cents. Calda Morley has no meaningful organic footprint to measure — that's the point.</t>
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Source: Ahrefs site-explorer-metrics, mode=subdomains, GB, 2026-08-01. Traffic value converted from USD cents.</t>
         </is>
       </c>
     </row>
